--- a/data-raw/datasets/microorganisms.codes.xlsx
+++ b/data-raw/datasets/microorganisms.codes.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>B_TRCHP_MNTG</t>
+          <t>F_TRCHP_MNTG</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>F_CPLLR</t>
+          <t>AN_CPLLR</t>
         </is>
       </c>
     </row>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="B1968" t="inlineStr">
         <is>
-          <t>F_STRMRL_MGNL</t>
+          <t>F_SRLLA_MGNL</t>
         </is>
       </c>
     </row>
@@ -25254,7 +25254,7 @@
       </c>
       <c r="B2074" t="inlineStr">
         <is>
-          <t>F_CPLLR_RKNS</t>
+          <t>AN_CPLLR_RKNS</t>
         </is>
       </c>
     </row>
@@ -39834,7 +39834,7 @@
       </c>
       <c r="B3289" t="inlineStr">
         <is>
-          <t>B_PSDLC_RFFN</t>
+          <t>B_PSDLCT_RFFN</t>
         </is>
       </c>
     </row>
@@ -41994,7 +41994,7 @@
       </c>
       <c r="B3469" t="inlineStr">
         <is>
-          <t>B_PSDLC_RFFN</t>
+          <t>B_PSDLCT_RFFN</t>
         </is>
       </c>
     </row>
@@ -43146,7 +43146,7 @@
       </c>
       <c r="B3565" t="inlineStr">
         <is>
-          <t>B_NRLLA_THRM</t>
+          <t>B_NEMRLL_THRM</t>
         </is>
       </c>
     </row>
@@ -43158,7 +43158,7 @@
       </c>
       <c r="B3566" t="inlineStr">
         <is>
-          <t>B_NRLLA_THRM</t>
+          <t>B_NEMRLL_THRM</t>
         </is>
       </c>
     </row>
@@ -45714,7 +45714,7 @@
       </c>
       <c r="B3779" t="inlineStr">
         <is>
-          <t>B_NRLLA</t>
+          <t>B_NEMRLL</t>
         </is>
       </c>
     </row>
@@ -48330,7 +48330,7 @@
       </c>
       <c r="B3997" t="inlineStr">
         <is>
-          <t>F_NECATR_AMRC</t>
+          <t>AN_NECTR_AMRC</t>
         </is>
       </c>
     </row>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="B4014" t="inlineStr">
         <is>
-          <t>F_NECATR</t>
+          <t>AN_NECTR</t>
         </is>
       </c>
     </row>
@@ -48546,7 +48546,7 @@
       </c>
       <c r="B4015" t="inlineStr">
         <is>
-          <t>F_NECATR_AMRC</t>
+          <t>AN_NECTR_AMRC</t>
         </is>
       </c>
     </row>
@@ -48558,7 +48558,7 @@
       </c>
       <c r="B4016" t="inlineStr">
         <is>
-          <t>F_NECATR</t>
+          <t>AN_NECTR</t>
         </is>
       </c>
     </row>
@@ -50514,7 +50514,7 @@
       </c>
       <c r="B4179" t="inlineStr">
         <is>
-          <t>B_ALTBC_LNGN</t>
+          <t>B_ALTBCT_LNGN</t>
         </is>
       </c>
     </row>
@@ -53526,7 +53526,7 @@
       </c>
       <c r="B4430" t="inlineStr">
         <is>
-          <t>B_ALTBC_LNGN</t>
+          <t>B_ALTBCT_LNGN</t>
         </is>
       </c>
     </row>
@@ -67734,7 +67734,7 @@
       </c>
       <c r="B5614" t="inlineStr">
         <is>
-          <t>B_TRCHP_TRCM</t>
+          <t>F_TRCHP_CNCN</t>
         </is>
       </c>
     </row>
@@ -67806,7 +67806,7 @@
       </c>
       <c r="B5620" t="inlineStr">
         <is>
-          <t>B_TRCHP_MNTG</t>
+          <t>F_TRCHP_MNTG</t>
         </is>
       </c>
     </row>
@@ -67878,7 +67878,7 @@
       </c>
       <c r="B5626" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -67890,7 +67890,7 @@
       </c>
       <c r="B5627" t="inlineStr">
         <is>
-          <t>B_TRCHP_SCHN</t>
+          <t>F_TRCHP_SCHN</t>
         </is>
       </c>
     </row>
@@ -67902,7 +67902,7 @@
       </c>
       <c r="B5628" t="inlineStr">
         <is>
-          <t>B_TRCHP_VLCM</t>
+          <t>F_TRCHP_VLCM</t>
         </is>
       </c>
     </row>
@@ -67938,7 +67938,7 @@
       </c>
       <c r="B5631" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -67962,7 +67962,7 @@
       </c>
       <c r="B5633" t="inlineStr">
         <is>
-          <t>B_TRCHP_VRRC</t>
+          <t>F_TRCHP_VRRC</t>
         </is>
       </c>
     </row>
@@ -68190,7 +68190,7 @@
       </c>
       <c r="B5652" t="inlineStr">
         <is>
-          <t>B_TRCHP_BNHM</t>
+          <t>F_TRCHP_BNHM</t>
         </is>
       </c>
     </row>
@@ -68250,7 +68250,7 @@
       </c>
       <c r="B5657" t="inlineStr">
         <is>
-          <t>B_TRCHP_TRCM</t>
+          <t>F_TRCHP_CNCN</t>
         </is>
       </c>
     </row>
@@ -68322,7 +68322,7 @@
       </c>
       <c r="B5663" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -68574,7 +68574,7 @@
       </c>
       <c r="B5684" t="inlineStr">
         <is>
-          <t>B_TRCHP_MNTG</t>
+          <t>F_TRCHP_MNTG</t>
         </is>
       </c>
     </row>
@@ -68586,7 +68586,7 @@
       </c>
       <c r="B5685" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -68730,7 +68730,7 @@
       </c>
       <c r="B5697" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -69198,7 +69198,7 @@
       </c>
       <c r="B5736" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -69234,7 +69234,7 @@
       </c>
       <c r="B5739" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -69246,7 +69246,7 @@
       </c>
       <c r="B5740" t="inlineStr">
         <is>
-          <t>B_TRCHP_TRCM</t>
+          <t>F_TRCHP_CNCN</t>
         </is>
       </c>
     </row>
@@ -69270,7 +69270,7 @@
       </c>
       <c r="B5742" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -69282,7 +69282,7 @@
       </c>
       <c r="B5743" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69294,7 +69294,7 @@
       </c>
       <c r="B5744" t="inlineStr">
         <is>
-          <t>B_TRCHP_FLVS</t>
+          <t>F_TRCHP_FLVS</t>
         </is>
       </c>
     </row>
@@ -69306,7 +69306,7 @@
       </c>
       <c r="B5745" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69318,7 +69318,7 @@
       </c>
       <c r="B5746" t="inlineStr">
         <is>
-          <t>B_TRCHP_GLOR</t>
+          <t>F_TRCHP_GLOR</t>
         </is>
       </c>
     </row>
@@ -69330,7 +69330,7 @@
       </c>
       <c r="B5747" t="inlineStr">
         <is>
-          <t>B_TRCHP_GLOR</t>
+          <t>F_TRCHP_GLOR</t>
         </is>
       </c>
     </row>
@@ -69354,7 +69354,7 @@
       </c>
       <c r="B5749" t="inlineStr">
         <is>
-          <t>B_TRCHP_MNTG</t>
+          <t>F_TRCHP_MNTG</t>
         </is>
       </c>
     </row>
@@ -69366,7 +69366,7 @@
       </c>
       <c r="B5750" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69390,7 +69390,7 @@
       </c>
       <c r="B5752" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69402,7 +69402,7 @@
       </c>
       <c r="B5753" t="inlineStr">
         <is>
-          <t>B_TRCHP_MNTG</t>
+          <t>F_TRCHP_MNTG</t>
         </is>
       </c>
     </row>
@@ -69414,7 +69414,7 @@
       </c>
       <c r="B5754" t="inlineStr">
         <is>
-          <t>B_TRCHP_PRLF</t>
+          <t>F_TRCHP_PRLF</t>
         </is>
       </c>
     </row>
@@ -69426,7 +69426,7 @@
       </c>
       <c r="B5755" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69438,7 +69438,7 @@
       </c>
       <c r="B5756" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69450,7 +69450,7 @@
       </c>
       <c r="B5757" t="inlineStr">
         <is>
-          <t>B_TRCHP_SCHN</t>
+          <t>F_TRCHP_SCHN</t>
         </is>
       </c>
     </row>
@@ -69462,7 +69462,7 @@
       </c>
       <c r="B5758" t="inlineStr">
         <is>
-          <t>B_TRCHP_SIMI</t>
+          <t>F_TRCHP_SIMI</t>
         </is>
       </c>
     </row>
@@ -69474,7 +69474,7 @@
       </c>
       <c r="B5759" t="inlineStr">
         <is>
-          <t>B_TRCHP_VLCM</t>
+          <t>F_TRCHP_VLCM</t>
         </is>
       </c>
     </row>
@@ -69498,7 +69498,7 @@
       </c>
       <c r="B5761" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -69522,7 +69522,7 @@
       </c>
       <c r="B5763" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -69546,7 +69546,7 @@
       </c>
       <c r="B5765" t="inlineStr">
         <is>
-          <t>B_TRCHP_VNBR</t>
+          <t>F_TRCHP_VNBR</t>
         </is>
       </c>
     </row>
@@ -69558,7 +69558,7 @@
       </c>
       <c r="B5766" t="inlineStr">
         <is>
-          <t>B_TRCHP_VRRC</t>
+          <t>F_TRCHP_VRRC</t>
         </is>
       </c>
     </row>
@@ -69570,7 +69570,7 @@
       </c>
       <c r="B5767" t="inlineStr">
         <is>
-          <t>B_TRCHP_VLCM</t>
+          <t>F_TRCHP_VLCM</t>
         </is>
       </c>
     </row>
@@ -69594,7 +69594,7 @@
       </c>
       <c r="B5769" t="inlineStr">
         <is>
-          <t>B_TRCHP_VLCM</t>
+          <t>F_TRCHP_VLCM</t>
         </is>
       </c>
     </row>
@@ -69810,7 +69810,7 @@
       </c>
       <c r="B5787" t="inlineStr">
         <is>
-          <t>B_TRCHP_RBRM</t>
+          <t>F_TRCHP_RBRM</t>
         </is>
       </c>
     </row>
@@ -69870,7 +69870,7 @@
       </c>
       <c r="B5792" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -69882,7 +69882,7 @@
       </c>
       <c r="B5793" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -69918,7 +69918,7 @@
       </c>
       <c r="B5796" t="inlineStr">
         <is>
-          <t>B_TRCHP_SCHN</t>
+          <t>F_TRCHP_SCHN</t>
         </is>
       </c>
     </row>
@@ -69990,7 +69990,7 @@
       </c>
       <c r="B5802" t="inlineStr">
         <is>
-          <t>B_TRCHP_SDNN</t>
+          <t>F_TRCHP_SDNN</t>
         </is>
       </c>
     </row>
@@ -70062,7 +70062,7 @@
       </c>
       <c r="B5808" t="inlineStr">
         <is>
-          <t>B_TRCHP_TNSR</t>
+          <t>F_TRCHP_TNSR</t>
         </is>
       </c>
     </row>
@@ -70302,7 +70302,7 @@
       </c>
       <c r="B5828" t="inlineStr">
         <is>
-          <t>B_TRCHP_VRRC</t>
+          <t>F_TRCHP_VRRC</t>
         </is>
       </c>
     </row>
@@ -70314,7 +70314,7 @@
       </c>
       <c r="B5829" t="inlineStr">
         <is>
-          <t>B_TRCHP_VLCM</t>
+          <t>F_TRCHP_VLCM</t>
         </is>
       </c>
     </row>
@@ -70350,7 +70350,7 @@
       </c>
       <c r="B5832" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -70362,7 +70362,7 @@
       </c>
       <c r="B5833" t="inlineStr">
         <is>
-          <t>B_TRCHP</t>
+          <t>F_TRCHP</t>
         </is>
       </c>
     </row>
@@ -70386,7 +70386,7 @@
       </c>
       <c r="B5835" t="inlineStr">
         <is>
-          <t>B_TRCHP_MNTG_INDT</t>
+          <t>F_TRCHP_INDT</t>
         </is>
       </c>
     </row>

--- a/data-raw/datasets/microorganisms.codes.xlsx
+++ b/data-raw/datasets/microorganisms.codes.xlsx
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>P_NCLSP_SLMN</t>
+          <t>F_NCLSPR_SLMN</t>
         </is>
       </c>
     </row>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="B2359" t="inlineStr">
         <is>
-          <t>P_ENCPH_BINS</t>
+          <t>F_ENCPH_BINS</t>
         </is>
       </c>
     </row>
@@ -29946,7 +29946,7 @@
       </c>
       <c r="B2465" t="inlineStr">
         <is>
-          <t>P_ENCPH</t>
+          <t>F_ENCPH</t>
         </is>
       </c>
     </row>
@@ -30858,7 +30858,7 @@
       </c>
       <c r="B2541" t="inlineStr">
         <is>
-          <t>P_EYTZN</t>
+          <t>F_EYTZN</t>
         </is>
       </c>
     </row>
@@ -49386,7 +49386,7 @@
       </c>
       <c r="B4085" t="inlineStr">
         <is>
-          <t>P_NOSEM</t>
+          <t>F_NOSEM</t>
         </is>
       </c>
     </row>
@@ -53562,7 +53562,7 @@
       </c>
       <c r="B4433" t="inlineStr">
         <is>
-          <t>P_PLSTP</t>
+          <t>F_PLSTP</t>
         </is>
       </c>
     </row>
@@ -61806,7 +61806,7 @@
       </c>
       <c r="B5120" t="inlineStr">
         <is>
-          <t>P_ENCPH</t>
+          <t>F_ENCPH</t>
         </is>
       </c>
     </row>
@@ -62862,7 +62862,7 @@
       </c>
       <c r="B5208" t="inlineStr">
         <is>
-          <t>P_ENCPH_INTS</t>
+          <t>F_ENCPH_INTS</t>
         </is>
       </c>
     </row>
